--- a/important_mails_2026-04-11.xlsx
+++ b/important_mails_2026-04-11.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,77 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
+          <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
+          <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Abbiamo rettificato il tuo saldo negativo di 285.13 € dovuto dal tuo account venditore Amazon.it in data aprile 11, 2026, utilizzando i fondi disponibili nei tuoi account Amazon.fr, Amazon.es. Puoi visualizzare il saldo del tuo account in qualsiasi momento accedendo al tuo account e quindi alla dashboard dei pagamenti .
+Per maggiori informazioni, vai a Rettifica del saldo negativo nei tuoi account .
+Distinti saluti,
+Amazon Payments Europe
+ Segnala un problema con questa e-mail
+ Per qualsiasi domanda consulta: Seller Central
+ Per modificare le preferenze sulle e-mail consulta: Preferenze sulle notifiche
+ Copyright 2026 Amazon, Inc. o società affiliate. Tutti i diritti riservati.
+ Amazon Payments Europe
+ 38 avenue John F. Kennedy,
+ L-1855 Lussemburgo,
+ Numero di registrazione in Lussemburgo: B-101818,
+ Capitale Sociale 165.833 EUR,
+ Numero di licenza di attività commerciale: 134248,
+ Partita IVA n. LU 20260743.
+ Questa e-mail è stata inviata da un indirizzo e-mail non monitorato.
+ SPC-EUAmazon-1301823410754995</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -540,39 +596,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -593,39 +649,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -640,39 +696,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -686,40 +742,40 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -736,39 +792,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -788,40 +844,40 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -839,39 +895,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -891,39 +947,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -944,39 +1000,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -997,40 +1053,40 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -1046,40 +1102,40 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -1097,39 +1153,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -1162,39 +1218,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -1209,39 +1265,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1260,39 +1316,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -1311,39 +1367,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -1355,39 +1411,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -1403,39 +1459,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -1447,39 +1503,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1494,39 +1550,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1538,39 +1594,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1582,39 +1638,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1626,39 +1682,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1670,39 +1726,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1714,39 +1770,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -1758,39 +1814,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1802,39 +1858,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -1846,39 +1902,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1890,39 +1946,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -1941,39 +1997,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -1985,39 +2041,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2029,39 +2085,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -2073,39 +2129,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2117,39 +2173,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -2161,39 +2217,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -2205,39 +2261,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -2249,39 +2305,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -2300,39 +2356,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -2344,40 +2400,40 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -2396,39 +2452,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -2440,39 +2496,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -2491,39 +2547,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -2555,39 +2611,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -2614,39 +2670,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -2658,39 +2714,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -2703,39 +2759,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -2751,39 +2807,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -2803,39 +2859,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -2854,39 +2910,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -2895,39 +2951,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2953,39 +3009,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3005,40 +3061,40 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -3054,39 +3110,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3106,39 +3162,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -3164,39 +3220,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3212,39 +3268,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3265,39 +3321,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -3311,40 +3367,40 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -3360,39 +3416,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3409,39 +3465,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -3464,39 +3520,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3516,39 +3572,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -3565,39 +3621,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3611,53 +3667,6 @@
  ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
 Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
 Te deseamos un éxit</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Balance Paid on Your Selling on Amazon payment account</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
- We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
- Please note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. In this case, we may continue to attempt charging your card until the remaining balance in your Amazon Selling on Amazon payment account is paid in full.
- You can also use the Make a Payment feature to repay the balance you owe. For details, refer “Making a Payment” in Seller Central Help.
- To view your payment activity anytime, please log in to your account and refer the Payments Report page.
- Thank you for selling on Amazon.
- Amazon Payments UK Limited
-Amazon Payments UK Limited, a private company limited by shares, is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60) with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom. Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
- Was this e-mail helpful?
- SPC-EUAma</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6470,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6476,69 +6485,21 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
+          <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Worten Marketplace - Portugal y España</t>
+          <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>¡Buenos días!
-Espero que te encuentres bien.
-Mi nombre es Gabriel Martins y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
-Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
-Sobre Worten.
-Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
-En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
-Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
-Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
-Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
-Worten Marketplace tiene una estrategia B2C,</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-09</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6559,39 +6520,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6614,39 +6575,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6667,39 +6628,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6723,39 +6684,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6778,39 +6739,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6833,39 +6794,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6887,39 +6848,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6937,39 +6898,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -6999,39 +6960,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7047,39 +7008,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7095,40 +7056,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7147,40 +7108,40 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
